--- a/Clustering/Lube Oil System/DBSCAN/clustering_lube_oil_g11/all_anomalies_sorted.xlsx
+++ b/Clustering/Lube Oil System/DBSCAN/clustering_lube_oil_g11/all_anomalies_sorted.xlsx
@@ -2531,7 +2531,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="B73" t="n">
         <v>0.38</v>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="B74" t="n">
         <v>0.55</v>
